--- a/Result/profitability/6486.xlsx
+++ b/Result/profitability/6486.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM50"/>
+  <dimension ref="A1:AM51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6780,6 +6780,133 @@
         <v>115.1</v>
       </c>
     </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>6486</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>572</v>
+      </c>
+      <c r="D51" t="n">
+        <v>435</v>
+      </c>
+      <c r="E51" t="n">
+        <v>136</v>
+      </c>
+      <c r="F51" t="n">
+        <v>23.83</v>
+      </c>
+      <c r="G51" t="n">
+        <v>21</v>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>3.63%</t>
+        </is>
+      </c>
+      <c r="I51" t="n">
+        <v>9</v>
+      </c>
+      <c r="J51" t="n">
+        <v>30</v>
+      </c>
+      <c r="K51" t="n">
+        <v>23</v>
+      </c>
+      <c r="L51" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="M51" t="n">
+        <v>1.255</v>
+      </c>
+      <c r="N51" t="n">
+        <v>31.545</v>
+      </c>
+      <c r="O51" t="n">
+        <v>0</v>
+      </c>
+      <c r="P51" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>0</v>
+      </c>
+      <c r="R51" t="n">
+        <v>0</v>
+      </c>
+      <c r="S51" t="n">
+        <v>0</v>
+      </c>
+      <c r="T51" t="n">
+        <v>0</v>
+      </c>
+      <c r="U51" t="n">
+        <v>1</v>
+      </c>
+      <c r="V51" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W51" t="n">
+        <v>-0.14</v>
+      </c>
+      <c r="X51" t="n">
+        <v>-0.2372881355932203</v>
+      </c>
+      <c r="Y51" t="n">
+        <v>-8.969999999999999</v>
+      </c>
+      <c r="Z51" t="n">
+        <v>-0.2734756097560975</v>
+      </c>
+      <c r="AA51" t="n">
+        <v>-0.53</v>
+      </c>
+      <c r="AB51" t="n">
+        <v>-0.5408163265306123</v>
+      </c>
+      <c r="AC51" t="n">
+        <v>-10.87</v>
+      </c>
+      <c r="AD51" t="n">
+        <v>-0.313256484149856</v>
+      </c>
+      <c r="AE51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ51" t="inlineStr">
+        <is>
+          <t>EPS衰退 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK51" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL51" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM51" t="n">
+        <v>115.2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
